--- a/data/reports/2024-09-16/2024-09-16_duplicates.xlsx
+++ b/data/reports/2024-09-16/2024-09-16_duplicates.xlsx
@@ -185,7 +185,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004139</t>
+    <t>RMD0009352</t>
   </si>
   <si>
     <t>Global Net Holdings, Inc.</t>
@@ -201,28 +201,28 @@
     <t>CEO</t>
   </si>
   <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t>800-7096314</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004139</t>
+  </si>
+  <si>
     <t>Sales</t>
   </si>
   <si>
     <t>800-709-6314</t>
   </si>
   <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009352</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t>800-7096314</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008972</t>
@@ -261,7 +261,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009084</t>
+    <t>RMD0009205</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,12 +318,6 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
-  </si>
-  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -346,7 +340,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008869</t>
+    <t>RMD0009084</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -409,7 +409,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004724</t>
+    <t>RMD0005819</t>
   </si>
   <si>
     <t>Ton80 Communications, LLC</t>
@@ -419,16 +419,16 @@
 Anderson SC 29642</t>
   </si>
   <si>
+    <t>4109121000</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004724</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005819</t>
-  </si>
-  <si>
-    <t>4109121000</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004849</t>
@@ -493,10 +493,37 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003758</t>
+  </si>
+  <si>
+    <t>Matchcom Telecommunications Inc.</t>
+  </si>
+  <si>
+    <t>1680 Michigan Ave
+Ste 700
+Miami Beach Florida 33139</t>
+  </si>
+  <si>
+    <t>Davon Person</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Network Operations Center</t>
+  </si>
+  <si>
+    <t>1250 E Hallandale Beach Blvd
+Hallandale FL 33009</t>
+  </si>
+  <si>
+    <t>9546248162</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007488</t>
-  </si>
-  <si>
-    <t>Matchcom Telecommunications Inc.</t>
   </si>
   <si>
     <t>1680 Michigan Ave
@@ -528,33 +555,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003758</t>
-  </si>
-  <si>
-    <t>1680 Michigan Ave
-Ste 700
-Miami Beach Florida 33139</t>
-  </si>
-  <si>
-    <t>Davon Person</t>
-  </si>
-  <si>
-    <t>Director of Operations</t>
-  </si>
-  <si>
-    <t>Network Operations Center</t>
-  </si>
-  <si>
-    <t>1250 E Hallandale Beach Blvd
-Hallandale FL 33009</t>
-  </si>
-  <si>
-    <t>9546248162</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005139</t>
@@ -711,7 +711,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -721,6 +721,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -739,13 +745,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005569</t>
+    <t>RMD0005461</t>
   </si>
   <si>
     <t>Valstarr Asia</t>
@@ -755,25 +755,10 @@
 Valley Center CA 92082</t>
   </si>
   <si>
+    <t>0031217672</t>
+  </si>
+  <si>
     <t>Vincent W. Kahn</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Systems Admin</t>
-  </si>
-  <si>
-    <t>'+13213288217</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005461</t>
-  </si>
-  <si>
-    <t>0031217672</t>
   </si>
   <si>
     <t>MANAGER</t>
@@ -793,7 +778,22 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
+    <t>RMD0005569</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Systems Admin</t>
+  </si>
+  <si>
+    <t>'+13213288217</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -806,25 +806,25 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Syed Omar Farooq Shah</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>'+61406851546</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005297</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
-  </si>
-  <si>
-    <t>Syed Omar Farooq Shah</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+61406851546</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
+    <t>RMD0005585</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -838,6 +838,28 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
+  </si>
+  <si>
+    <t>Paul Joncas</t>
+  </si>
+  <si>
+    <t>Operatopms</t>
+  </si>
+  <si>
+    <t>187 Plymouth Avenue
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005574</t>
+  </si>
+  <si>
     <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
   </si>
   <si>
@@ -845,29 +867,20 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005585</t>
-  </si>
-  <si>
-    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
-  </si>
-  <si>
-    <t>Paul Joncas</t>
-  </si>
-  <si>
-    <t>Operatopms</t>
-  </si>
-  <si>
-    <t>187 Plymouth Avenue
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
+    <t>RMD0006284</t>
+  </si>
+  <si>
+    <t>Office No 17 3rd Floor Anique Arcade Plaza I8 Markaz
+  Islamabad, Pakistan</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -877,9 +890,6 @@
 federal 46000 Islamabad, Pakistan</t>
   </si>
   <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
     <t>Umair Hassan</t>
   </si>
   <si>
@@ -890,16 +900,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8037e23e1b32781093d3a820f54bcb1c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006284</t>
-  </si>
-  <si>
-    <t>Office No 17 3rd Floor Anique Arcade Plaza I8 Markaz
-  Islamabad, Pakistan</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008125</t>
@@ -931,7 +931,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007626</t>
+    <t>RMD0007575</t>
   </si>
   <si>
     <t>Turcios Parada SA</t>
@@ -944,16 +944,16 @@
     <t>El Salvador</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007626</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007575</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007716</t>
+    <t>RMD0007696</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -963,16 +963,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007716</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -982,6 +982,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -997,13 +1003,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008423</t>
+    <t>RMD0008393</t>
   </si>
   <si>
     <t>Your Business I.T. Inc.</t>
@@ -1011,6 +1011,12 @@
   <si>
     <t>295 Weber St. N
 Ontario N2J 3H8 Waterloo, Canada</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008423</t>
   </si>
   <si>
     <t>Your Business I.T.</t>
@@ -1028,13 +1034,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=761bc9e71b3eb810d39dddb6bc4bcbe0&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008393</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1044,12 +1044,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1057,7 +1051,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008610</t>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008612</t>
   </si>
   <si>
     <t>Liberty Wealth Planners</t>
@@ -1067,43 +1067,49 @@
  110065 Dehli, India</t>
   </si>
   <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008611</t>
+  </si>
+  <si>
     <t>Bangladesh</t>
   </si>
   <si>
+    <t>Nobe</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008610</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008611</t>
-  </si>
-  <si>
-    <t>Nobe</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008759</t>
+    <t>RMD0008756</t>
   </si>
   <si>
     <t>573 Ocean Blvd
 Hampton NH 03842</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008759</t>
+  </si>
+  <si>
     <t>Jeffrey D Houston</t>
   </si>
   <si>
@@ -1116,13 +1122,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=46724d021b0b3050003c43f1f54bcb05&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008756</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008755</t>
+    <t>RMD0008798</t>
   </si>
   <si>
     <t>Aspire Holdings Group LLC</t>
@@ -1135,30 +1135,30 @@
     <t>AspirePBX</t>
   </si>
   <si>
+    <t>CP Short</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>6023888700</t>
+  </si>
+  <si>
+    <t>725</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008755</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=82b1054a1b0f30508d57ecace54bcbda&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008798</t>
-  </si>
-  <si>
-    <t>CP Short</t>
-  </si>
-  <si>
-    <t>Member</t>
-  </si>
-  <si>
-    <t>Partner</t>
-  </si>
-  <si>
-    <t>6023888700</t>
-  </si>
-  <si>
-    <t>725</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0008787</t>
   </si>
   <si>
@@ -1186,7 +1186,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=29f1aec61b0f3050003c43f1f54bcba5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009161</t>
+    <t>RMD0009160</t>
   </si>
   <si>
     <t>MCE Systems</t>
@@ -1196,16 +1196,16 @@
 Irvine CA 92604</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009161</t>
+  </si>
+  <si>
     <t>9497014500</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009160</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009453</t>
@@ -6358,9 +6358,15 @@
       <c r="F7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J7" s="1" t="s">
         <v>58</v>
       </c>
@@ -6418,15 +6424,9 @@
       <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
         <v>58</v>
       </c>
@@ -6601,9 +6601,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>34</v>
@@ -6614,14 +6616,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6648,7 +6652,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6657,13 +6661,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>34</v>
@@ -6674,9 +6676,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6695,41 +6695,55 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
+      <c r="Q13" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R13" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6741,46 +6755,32 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>102</v>
-      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q14" s="1"/>
       <c r="R14" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6806,54 +6806,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6870,33 +6856,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -7015,16 +7015,28 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="M19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+        <v>127</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="Q19" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R19" s="1" t="s">
         <v>26</v>
       </c>
@@ -7032,16 +7044,16 @@
         <v>26</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U19" s="1"/>
       <c r="V19" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" s="1">
         <v>25462672</v>
@@ -7061,28 +7073,16 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>130</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1" t="s">
         <v>26</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>26</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1" t="s">
@@ -7335,31 +7335,27 @@
       <c r="O25" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B26" s="1">
         <v>27710730</v>
@@ -7368,7 +7364,7 @@
         <v>152</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>26</v>
@@ -7380,37 +7376,41 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="M26" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="N26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="P26" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U26" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U26" s="1"/>
       <c r="V26" s="1" t="s">
         <v>169</v>
       </c>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>34</v>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>34</v>
@@ -7874,48 +7874,34 @@
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>222</v>
-      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>223</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q35" s="1"/>
       <c r="R35" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U35" s="1"/>
       <c r="V35" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B36" s="1">
         <v>31124688</v>
@@ -7934,25 +7920,39 @@
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
+      <c r="I36" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="M36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
+        <v>218</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
+      <c r="Q36" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R36" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1" t="s">
@@ -7978,48 +7978,54 @@
       <c r="F37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="G37" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J37" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B38" s="1">
         <v>31217029</v>
@@ -8036,26 +8042,20 @@
       <c r="F38" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>27</v>
@@ -8065,16 +8065,16 @@
       </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8103,33 +8103,45 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="M39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
+        <v>244</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>248</v>
+      </c>
       <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
+      <c r="Q39" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R39" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B40" s="1">
         <v>31294614</v>
@@ -8149,36 +8161,24 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>189</v>
-      </c>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>250</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
       <c r="P40" s="1"/>
-      <c r="Q40" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q40" s="1"/>
       <c r="R40" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U40" s="1"/>
       <c r="V40" s="1" t="s">
@@ -8210,42 +8210,48 @@
       <c r="H41" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="M41" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="1" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U41" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V41" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B42" s="1">
         <v>31356652</v>
@@ -8266,18 +8272,14 @@
         <v>255</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L42" s="1" t="s">
         <v>263</v>
       </c>
+      <c r="I42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
       <c r="M42" s="1" t="s">
         <v>264</v>
       </c>
@@ -8285,24 +8287,22 @@
         <v>27</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="1" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
         <v>265</v>
       </c>
@@ -8324,55 +8324,49 @@
       <c r="F43" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>270</v>
-      </c>
+      <c r="G43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
       <c r="M43" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>271</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
       <c r="P43" s="1"/>
-      <c r="Q43" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q43" s="1"/>
       <c r="R43" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B44" s="1">
         <v>31392434</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>34</v>
@@ -8380,33 +8374,39 @@
       <c r="F44" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="M44" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
+        <v>271</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>274</v>
+      </c>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
+      <c r="Q44" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
@@ -8454,7 +8454,7 @@
         <v>281</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>33</v>
@@ -8544,9 +8544,7 @@
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
-      <c r="M47" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -8590,7 +8588,9 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
+      <c r="M48" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
@@ -8628,15 +8628,9 @@
       <c r="F49" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -8680,9 +8674,15 @@
       <c r="F50" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+      <c r="G50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -8721,55 +8721,41 @@
         <v>300</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-      <c r="J51" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
       <c r="R51" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U51" s="1"/>
       <c r="V51" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B52" s="1">
         <v>31445216</v>
@@ -8781,32 +8767,46 @@
         <v>300</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
+      <c r="J52" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M52" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
+        <v>300</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R52" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S52" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U52" s="1"/>
       <c r="V52" s="1" t="s">
@@ -8835,43 +8835,33 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>313</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
       <c r="P53" s="1"/>
-      <c r="Q53" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B54" s="1">
         <v>31455868</v>
@@ -8891,24 +8881,34 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
+        <v>314</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+      <c r="Q54" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8941,7 +8941,7 @@
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1" t="s">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
@@ -8958,12 +8958,12 @@
       </c>
       <c r="U55" s="1"/>
       <c r="V55" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B56" s="1">
         <v>31457815</v>
@@ -8987,7 +8987,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="s">
-        <v>322</v>
+        <v>40</v>
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
@@ -9029,33 +9029,45 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
+      <c r="J57" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="M57" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
+        <v>326</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
+      <c r="Q57" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R57" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B58" s="1">
         <v>31475270</v>
@@ -9070,50 +9082,40 @@
         <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="I58" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>332</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
       <c r="P58" s="1"/>
-      <c r="Q58" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q58" s="1"/>
       <c r="R58" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U58" s="1"/>
       <c r="V58" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="59" spans="1:22">
       <c r="A59" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B59" s="1">
         <v>31475270</v>
@@ -9128,13 +9130,11 @@
         <v>34</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="1" t="s">
-        <v>335</v>
-      </c>
+      <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -9171,53 +9171,41 @@
         <v>338</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
       <c r="R60" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B61" s="1">
         <v>31485048</v>
@@ -9227,32 +9215,44 @@
         <v>338</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
+      <c r="J61" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
+        <v>338</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R61" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9273,43 +9273,57 @@
         <v>347</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
         <v>348</v>
       </c>
       <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
+      <c r="J62" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>351</v>
+      </c>
       <c r="M62" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
+        <v>347</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q62" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R62" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U62" s="1"/>
       <c r="V62" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:22">
       <c r="A63" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B63" s="1">
         <v>31489362</v>
@@ -9321,48 +9335,34 @@
         <v>347</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
         <v>348</v>
       </c>
       <c r="I63" s="1"/>
-      <c r="J63" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>353</v>
-      </c>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
       <c r="M63" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="P63" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
       <c r="R63" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U63" s="1"/>
       <c r="V63" s="1" t="s">
@@ -9412,7 +9412,7 @@
         <v>362</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q64" s="1" t="s">
         <v>33</v>
@@ -9493,49 +9493,39 @@
         <v>368</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="J66" s="1" t="s">
-        <v>367</v>
-      </c>
+      <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
-      <c r="M66" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
       <c r="P66" s="1"/>
-      <c r="Q66" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="Q66" s="1"/>
       <c r="R66" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U66" s="1"/>
       <c r="V66" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="67" spans="1:22">
       <c r="A67" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B67" s="1">
         <v>31544182</v>
@@ -9547,30 +9537,40 @@
         <v>368</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+      <c r="J67" s="1" t="s">
+        <v>367</v>
+      </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
+      <c r="M67" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
+      <c r="Q67" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R67" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U67" s="1"/>
       <c r="V67" s="1" t="s">
@@ -9647,7 +9647,7 @@
         <v>379</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>380</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="P69" s="1"/>
       <c r="Q69" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>34</v>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>34</v>
@@ -9805,7 +9805,7 @@
         <v>394</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>395</v>
@@ -9925,10 +9925,10 @@
         <v>409</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M74" s="1" t="s">
         <v>407</v>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="P74" s="1"/>
       <c r="Q74" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R74" s="1" t="s">
         <v>34</v>
@@ -10033,7 +10033,7 @@
         <v>418</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>380</v>
@@ -10155,10 +10155,10 @@
         <v>433</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>431</v>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="P78" s="1"/>
       <c r="Q78" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>34</v>
@@ -10211,7 +10211,7 @@
         <v>438</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>439</v>
@@ -10233,7 +10233,7 @@
       </c>
       <c r="P79" s="1"/>
       <c r="Q79" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R79" s="1" t="s">
         <v>34</v>
@@ -10275,7 +10275,7 @@
         <v>447</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L80" s="1"/>
       <c r="M80" s="1" t="s">
@@ -10331,10 +10331,10 @@
         <v>453</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>454</v>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="P81" s="1"/>
       <c r="Q81" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R81" s="1" t="s">
         <v>34</v>
@@ -10435,10 +10435,10 @@
         <v>462</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M83" s="1"/>
       <c r="N83" s="1" t="s">
@@ -10491,7 +10491,7 @@
         <v>468</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L84" s="1"/>
       <c r="M84" s="1" t="s">
@@ -10534,7 +10534,7 @@
         <v>34</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
@@ -10645,7 +10645,7 @@
         <v>483</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>484</v>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="P88" s="1"/>
       <c r="Q88" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R88" s="1" t="s">
         <v>26</v>
@@ -10759,13 +10759,13 @@
         <v>27</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>500</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>501</v>
@@ -10774,7 +10774,7 @@
         <v>502</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>499</v>
@@ -10829,10 +10829,10 @@
         <v>508</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>509</v>
@@ -10891,10 +10891,10 @@
         <v>515</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>513</v>
@@ -10952,7 +10952,7 @@
         <v>522</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>519</v>
@@ -11098,7 +11098,7 @@
         <v>34</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>28</v>
@@ -11122,7 +11122,7 @@
         <v>535</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>539</v>
@@ -11158,7 +11158,7 @@
         <v>34</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>28</v>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>34</v>
@@ -11366,7 +11366,7 @@
         <v>59</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>559</v>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="P100" s="1"/>
       <c r="Q100" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R100" s="1" t="s">
         <v>34</v>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="P101" s="1"/>
       <c r="Q101" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R101" s="1" t="s">
         <v>34</v>
@@ -11475,13 +11475,13 @@
         <v>27</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>570</v>
@@ -11490,7 +11490,7 @@
         <v>59</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M102" s="1" t="s">
         <v>569</v>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="P102" s="1"/>
       <c r="Q102" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>34</v>
@@ -11532,7 +11532,7 @@
         <v>34</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
@@ -11641,7 +11641,7 @@
         <v>585</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L105" s="1" t="s">
         <v>31</v>
@@ -11703,7 +11703,7 @@
         <v>591</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L106" s="1" t="s">
         <v>592</v>
@@ -11801,13 +11801,13 @@
         <v>27</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J108" s="1" t="s">
         <v>603</v>
@@ -11967,7 +11967,7 @@
         <v>619</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>620</v>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="P111" s="1"/>
       <c r="Q111" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>34</v>
@@ -12087,10 +12087,10 @@
         <v>635</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>633</v>
@@ -12197,7 +12197,7 @@
         <v>645</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>646</v>
@@ -12256,7 +12256,7 @@
         <v>59</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M116" s="1" t="s">
         <v>651</v>
@@ -12315,7 +12315,7 @@
         <v>659</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L117" s="1" t="s">
         <v>660</v>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P118" s="1"/>
       <c r="Q118" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R118" s="1" t="s">
         <v>34</v>
@@ -12433,10 +12433,10 @@
         <v>673</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M119" s="1"/>
       <c r="N119" s="1" t="s">
@@ -12497,7 +12497,7 @@
         <v>681</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L120" s="1"/>
       <c r="M120" s="1" t="s">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="P120" s="1"/>
       <c r="Q120" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R120" s="1" t="s">
         <v>26</v>
@@ -12719,10 +12719,10 @@
         <v>703</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M124" s="1" t="s">
         <v>702</v>
@@ -12777,10 +12777,10 @@
         <v>709</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>708</v>
@@ -12835,7 +12835,7 @@
         <v>715</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L126" s="1" t="s">
         <v>716</v>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="P127" s="1"/>
       <c r="Q127" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R127" s="1" t="s">
         <v>34</v>
@@ -13054,7 +13054,7 @@
         <v>740</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>737</v>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="P131" s="1"/>
       <c r="Q131" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R131" s="1" t="s">
         <v>34</v>
@@ -13229,10 +13229,10 @@
         <v>759</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>758</v>
@@ -13333,10 +13333,10 @@
         <v>770</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M135" s="1" t="s">
         <v>768</v>
@@ -13429,7 +13429,7 @@
         <v>778</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L137" s="1" t="s">
         <v>779</v>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="P137" s="1"/>
       <c r="Q137" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R137" s="1" t="s">
         <v>34</v>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="P139" s="1"/>
       <c r="Q139" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R139" s="1" t="s">
         <v>34</v>
@@ -13698,7 +13698,7 @@
         <v>807</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M142" s="1" t="s">
         <v>808</v>
@@ -13801,7 +13801,7 @@
         <v>818</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L144" s="1" t="s">
         <v>819</v>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="P144" s="1"/>
       <c r="Q144" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R144" s="1" t="s">
         <v>34</v>
@@ -13875,7 +13875,7 @@
         <v>828</v>
       </c>
       <c r="Q145" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R145" s="1" t="s">
         <v>26</v>
@@ -13978,7 +13978,7 @@
         <v>59</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M147" s="1"/>
       <c r="N147" s="1" t="s">
@@ -14214,7 +14214,7 @@
         <v>493</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M152" s="1"/>
       <c r="N152" s="1" t="s">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="P152" s="1"/>
       <c r="Q152" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R152" s="1" t="s">
         <v>34</v>
@@ -14270,7 +14270,7 @@
         <v>868</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M153" s="1"/>
       <c r="N153" s="1" t="s">
@@ -14323,7 +14323,7 @@
         <v>874</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L154" s="1" t="s">
         <v>875</v>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="P157" s="1"/>
       <c r="Q157" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R157" s="1" t="s">
         <v>34</v>
@@ -14560,7 +14560,7 @@
         <v>34</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
@@ -14569,14 +14569,14 @@
         <v>898</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>189</v>
       </c>
       <c r="M159" s="1"/>
       <c r="N159" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O159" s="1" t="s">
         <v>899</v>
@@ -14945,7 +14945,7 @@
         <v>27</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>935</v>
@@ -15004,7 +15004,7 @@
         <v>34</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>28</v>
@@ -15028,7 +15028,7 @@
         <v>944</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O167" s="1" t="s">
         <v>945</v>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P168" s="1"/>
       <c r="Q168" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>26</v>
@@ -15127,7 +15127,7 @@
         <v>27</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H169" s="1"/>
       <c r="I169" s="1"/>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="P170" s="1"/>
       <c r="Q170" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R170" s="1" t="s">
         <v>34</v>
@@ -15242,7 +15242,7 @@
         <v>968</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M171" s="1"/>
       <c r="N171" s="1" t="s">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="P173" s="1"/>
       <c r="Q173" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>34</v>
@@ -15405,14 +15405,14 @@
         <v>27</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H174" s="1" t="s">
         <v>989</v>
       </c>
       <c r="I174" s="1"/>
       <c r="J174" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K174" s="1" t="s">
         <v>59</v>
@@ -15519,7 +15519,7 @@
         <v>996</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L176" s="1" t="s">
         <v>997</v>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="P176" s="1"/>
       <c r="Q176" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R176" s="1" t="s">
         <v>34</v>
@@ -15577,10 +15577,10 @@
         <v>1001</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>1002</v>
@@ -15638,7 +15638,7 @@
         <v>59</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M178" s="1" t="s">
         <v>1006</v>
@@ -15696,7 +15696,7 @@
         <v>1015</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M179" s="1" t="s">
         <v>1016</v>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="P181" s="1"/>
       <c r="Q181" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R181" s="1" t="s">
         <v>34</v>
@@ -15856,7 +15856,7 @@
         <v>34</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G182" s="1"/>
       <c r="H182" s="1"/>
@@ -15874,14 +15874,14 @@
         <v>1037</v>
       </c>
       <c r="N182" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O182" s="1" t="s">
         <v>1038</v>
       </c>
       <c r="P182" s="1"/>
       <c r="Q182" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>34</v>
@@ -15923,10 +15923,10 @@
         <v>1043</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M183" s="1" t="s">
         <v>1041</v>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="P183" s="1"/>
       <c r="Q183" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R183" s="1" t="s">
         <v>26</v>
@@ -15997,7 +15997,7 @@
       </c>
       <c r="P184" s="1"/>
       <c r="Q184" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R184" s="1" t="s">
         <v>26</v>
@@ -16093,13 +16093,13 @@
         <v>27</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H186" s="1" t="s">
         <v>1065</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
@@ -16333,7 +16333,7 @@
         <v>1090</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L190" s="1" t="s">
         <v>31</v>
@@ -16391,10 +16391,10 @@
         <v>1097</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M191" s="1"/>
       <c r="N191" s="1" t="s">
@@ -16453,7 +16453,7 @@
         <v>1104</v>
       </c>
       <c r="K192" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L192" s="1" t="s">
         <v>1105</v>
@@ -16791,7 +16791,7 @@
         <v>1143</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L198" s="1" t="s">
         <v>189</v>
@@ -16847,7 +16847,7 @@
         <v>1149</v>
       </c>
       <c r="K199" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L199" s="1" t="s">
         <v>604</v>
@@ -16910,7 +16910,7 @@
         <v>1157</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M200" s="1" t="s">
         <v>1153</v>
@@ -16967,10 +16967,10 @@
         <v>1164</v>
       </c>
       <c r="K201" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L201" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M201" s="1" t="s">
         <v>1165</v>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="P201" s="1"/>
       <c r="Q201" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R201" s="1" t="s">
         <v>34</v>
@@ -17025,7 +17025,7 @@
         <v>1170</v>
       </c>
       <c r="K202" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L202" s="1" t="s">
         <v>189</v>
@@ -17071,13 +17071,13 @@
         <v>27</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H203" s="1" t="s">
         <v>1173</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J203" s="1"/>
       <c r="K203" s="1"/>
@@ -17114,7 +17114,7 @@
         <v>34</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G204" s="1"/>
       <c r="H204" s="1"/>
@@ -17132,14 +17132,14 @@
         <v>1178</v>
       </c>
       <c r="N204" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O204" s="1" t="s">
         <v>1179</v>
       </c>
       <c r="P204" s="1"/>
       <c r="Q204" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R204" s="1" t="s">
         <v>34</v>
@@ -17183,7 +17183,7 @@
         <v>1185</v>
       </c>
       <c r="K205" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L205" s="1" t="s">
         <v>189</v>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="P207" s="1"/>
       <c r="Q207" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R207" s="1" t="s">
         <v>34</v>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="P208" s="1"/>
       <c r="Q208" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R208" s="1" t="s">
         <v>34</v>
@@ -17423,7 +17423,7 @@
         <v>1218</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L209" s="1" t="s">
         <v>1219</v>
@@ -17487,7 +17487,7 @@
         <v>1218</v>
       </c>
       <c r="K210" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L210" s="1" t="s">
         <v>1219</v>
@@ -17541,13 +17541,13 @@
         <v>185</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J211" s="1" t="s">
         <v>1232</v>
@@ -17739,10 +17739,10 @@
         <v>1251</v>
       </c>
       <c r="K214" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M214" s="1" t="s">
         <v>1252</v>
@@ -17817,7 +17817,7 @@
       </c>
       <c r="P215" s="1"/>
       <c r="Q215" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R215" s="1" t="s">
         <v>34</v>
@@ -17877,7 +17877,7 @@
       </c>
       <c r="P216" s="1"/>
       <c r="Q216" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R216" s="1" t="s">
         <v>34</v>
@@ -17913,7 +17913,7 @@
         <v>1102</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H217" s="1"/>
       <c r="I217" s="1"/>
@@ -18027,7 +18027,7 @@
         <v>1276</v>
       </c>
       <c r="K219" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L219" s="1" t="s">
         <v>189</v>
@@ -18156,7 +18156,7 @@
         <v>1289</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M221" s="1" t="s">
         <v>1290</v>
@@ -18216,7 +18216,7 @@
         <v>1297</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M222" s="1" t="s">
         <v>1298</v>
@@ -18274,7 +18274,7 @@
         <v>1306</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M223" s="1" t="s">
         <v>1303</v>
@@ -18347,7 +18347,7 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R224" s="1" t="s">
         <v>26</v>
@@ -18705,10 +18705,10 @@
         <v>1354</v>
       </c>
       <c r="K230" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M230" s="1" t="s">
         <v>1355</v>
@@ -18759,13 +18759,13 @@
         <v>27</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H231" s="1" t="s">
         <v>1360</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J231" s="1" t="s">
         <v>1361</v>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P231" s="1"/>
       <c r="Q231" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R231" s="1" t="s">
         <v>34</v>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>34</v>
@@ -19093,7 +19093,7 @@
         <v>1401</v>
       </c>
       <c r="K236" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L236" s="1" t="s">
         <v>1402</v>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="P238" s="1"/>
       <c r="Q238" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R238" s="1" t="s">
         <v>34</v>
@@ -19530,7 +19530,7 @@
         <v>1452</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M243" s="1" t="s">
         <v>1448</v>
@@ -19651,10 +19651,10 @@
         <v>1464</v>
       </c>
       <c r="K245" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M245" s="1" t="s">
         <v>1463</v>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="P245" s="1"/>
       <c r="Q245" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R245" s="1" t="s">
         <v>34</v>
@@ -19765,22 +19765,22 @@
         <v>27</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J247" s="1" t="s">
         <v>1475</v>
       </c>
       <c r="K247" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M247" s="1" t="s">
         <v>1474</v>
@@ -19835,10 +19835,10 @@
         <v>1475</v>
       </c>
       <c r="K248" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>1479</v>
@@ -20026,7 +20026,7 @@
         <v>280</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M251" s="1" t="s">
         <v>1502</v>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="P251" s="1"/>
       <c r="Q251" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R251" s="1" t="s">
         <v>34</v>
@@ -20088,7 +20088,7 @@
         <v>280</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M252" s="1" t="s">
         <v>1502</v>
@@ -20101,7 +20101,7 @@
       </c>
       <c r="P252" s="1"/>
       <c r="Q252" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R252" s="1" t="s">
         <v>34</v>
@@ -20221,7 +20221,7 @@
       </c>
       <c r="P254" s="1"/>
       <c r="Q254" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R254" s="1" t="s">
         <v>34</v>
@@ -20630,7 +20630,7 @@
         <v>1568</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M261" s="1" t="s">
         <v>1569</v>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="P261" s="1"/>
       <c r="Q261" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R261" s="1" t="s">
         <v>34</v>
@@ -20694,7 +20694,7 @@
         <v>1568</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M262" s="1" t="s">
         <v>1574</v>
@@ -20707,7 +20707,7 @@
       </c>
       <c r="P262" s="1"/>
       <c r="Q262" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R262" s="1" t="s">
         <v>34</v>
@@ -20754,7 +20754,7 @@
         <v>493</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M263" s="1" t="s">
         <v>1583</v>
@@ -20767,7 +20767,7 @@
       </c>
       <c r="P263" s="1"/>
       <c r="Q263" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R263" s="1" t="s">
         <v>34</v>
@@ -20927,13 +20927,13 @@
         <v>27</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H266" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J266" s="1" t="s">
         <v>1602</v>
@@ -21019,7 +21019,7 @@
       </c>
       <c r="P267" s="1"/>
       <c r="Q267" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R267" s="1" t="s">
         <v>34</v>
@@ -21079,7 +21079,7 @@
       </c>
       <c r="P268" s="1"/>
       <c r="Q268" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R268" s="1" t="s">
         <v>34</v>
@@ -21130,7 +21130,7 @@
         <v>740</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1627</v>
@@ -21192,7 +21192,7 @@
         <v>740</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M270" s="1" t="s">
         <v>1627</v>
@@ -21256,7 +21256,7 @@
         <v>59</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M271" s="1" t="s">
         <v>1639</v>
@@ -21320,7 +21320,7 @@
         <v>59</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M272" s="1" t="s">
         <v>1648</v>
@@ -21369,13 +21369,13 @@
         <v>195</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H273" s="1" t="s">
         <v>1655</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>1656</v>
@@ -21399,7 +21399,7 @@
         <v>1660</v>
       </c>
       <c r="Q273" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R273" s="1" t="s">
         <v>34</v>
@@ -21437,13 +21437,13 @@
         <v>195</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H274" s="1" t="s">
         <v>1655</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>1656</v>
@@ -21467,7 +21467,7 @@
         <v>1660</v>
       </c>
       <c r="Q274" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R274" s="1" t="s">
         <v>34</v>
@@ -21516,7 +21516,7 @@
         <v>1369</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M275" s="1" t="s">
         <v>1670</v>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="P275" s="1"/>
       <c r="Q275" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R275" s="1" t="s">
         <v>34</v>
@@ -21651,7 +21651,7 @@
       </c>
       <c r="P277" s="1"/>
       <c r="Q277" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R277" s="1" t="s">
         <v>34</v>
@@ -21713,7 +21713,7 @@
       </c>
       <c r="P278" s="1"/>
       <c r="Q278" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R278" s="1" t="s">
         <v>34</v>
@@ -22248,7 +22248,7 @@
         <v>1758</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M287" s="1" t="s">
         <v>1755</v>
@@ -22261,7 +22261,7 @@
       </c>
       <c r="P287" s="1"/>
       <c r="Q287" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R287" s="1" t="s">
         <v>34</v>
@@ -22306,7 +22306,7 @@
         <v>1763</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M288" s="1" t="s">
         <v>1755</v>
@@ -22319,7 +22319,7 @@
       </c>
       <c r="P288" s="1"/>
       <c r="Q288" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R288" s="1" t="s">
         <v>34</v>
